--- a/artfynd/A 2518-2023 artfynd.xlsx
+++ b/artfynd/A 2518-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2518-2023 artfynd.xlsx
+++ b/artfynd/A 2518-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106908224</v>
+        <v>106908131</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,7 +703,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550522.2102826363</v>
+        <v>550632</v>
       </c>
       <c r="R2" t="n">
-        <v>6386021.557929825</v>
+        <v>6385963</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,19 +755,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106908167</v>
+        <v>106908150</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -829,7 +813,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -844,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550552.8604763909</v>
+        <v>550532</v>
       </c>
       <c r="R3" t="n">
-        <v>6386017.118645364</v>
+        <v>6386036</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,19 +865,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106908234</v>
+        <v>106908159</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550543.9508489654</v>
+        <v>550517</v>
       </c>
       <c r="R4" t="n">
-        <v>6385999.864580221</v>
+        <v>6386025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,19 +975,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1042,15 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>106908213</v>
+        <v>106908167</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,11 +1033,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1094,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550507.1435345405</v>
+        <v>550553</v>
       </c>
       <c r="R5" t="n">
-        <v>6386024.584448203</v>
+        <v>6386017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1127,19 +1081,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1167,15 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>106908131</v>
+        <v>106908179</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1202,7 +1141,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1219,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550632.4399080996</v>
+        <v>550500</v>
       </c>
       <c r="R6" t="n">
-        <v>6385962.932794119</v>
+        <v>6386043</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,19 +1191,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,15 +1221,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>106908150</v>
+        <v>106908189</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,11 +1249,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1344,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550531.6966842859</v>
+        <v>550506</v>
       </c>
       <c r="R7" t="n">
-        <v>6386035.60476388</v>
+        <v>6386059</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,19 +1297,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,12 +1330,7 @@
         <v>106908197</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,10 +1374,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550488.710022738</v>
+        <v>550489</v>
       </c>
       <c r="R8" t="n">
-        <v>6386039.354783437</v>
+        <v>6386039</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,19 +1407,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,15 +1437,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>106908159</v>
+        <v>106908213</v>
       </c>
       <c r="B9" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1577,7 +1467,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1594,10 +1484,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550516.8035492453</v>
+        <v>550507</v>
       </c>
       <c r="R9" t="n">
-        <v>6386024.704832119</v>
+        <v>6386025</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1627,19 +1517,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1667,15 +1547,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>106908179</v>
+        <v>106908224</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1700,11 +1575,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1719,10 +1590,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550500.4699489778</v>
+        <v>550522</v>
       </c>
       <c r="R10" t="n">
-        <v>6386043.251276329</v>
+        <v>6386022</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,19 +1623,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,15 +1653,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>106908261</v>
+        <v>106908234</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,7 +1683,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1844,10 +1700,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550512.0603181153</v>
+        <v>550544</v>
       </c>
       <c r="R11" t="n">
-        <v>6386017.681417519</v>
+        <v>6386000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1877,19 +1733,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,15 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>106908189</v>
+        <v>106908261</v>
       </c>
       <c r="B12" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1950,7 +1791,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -1965,10 +1810,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550505.6363705947</v>
+        <v>550512</v>
       </c>
       <c r="R12" t="n">
-        <v>6386059.386994059</v>
+        <v>6386018</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1998,19 +1843,9 @@
           <t>2023-02-21</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-02-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2038,15 +1873,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>108193178</v>
+        <v>108193121</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2073,7 +1903,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2090,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550528.9999993561</v>
+        <v>550529</v>
       </c>
       <c r="R13" t="n">
-        <v>6386036.642572363</v>
+        <v>6386049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,19 +1953,9 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,15 +1983,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>108193455</v>
+        <v>108193178</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2198,7 +2013,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2215,10 +2030,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550645.2946129543</v>
+        <v>550529</v>
       </c>
       <c r="R14" t="n">
-        <v>6386008.09392691</v>
+        <v>6386037</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2248,24 +2063,9 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tyvärr på nyupptaget hygge. Ingen hänsyn tagen trots vetskap om växtlokalen!</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2293,15 +2093,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>108193121</v>
+        <v>108193455</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2328,7 +2123,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2345,10 +2140,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550528.846420511</v>
+        <v>550645</v>
       </c>
       <c r="R15" t="n">
-        <v>6386048.962049755</v>
+        <v>6386008</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2378,19 +2173,14 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Tyvärr på nyupptaget hygge. Ingen hänsyn tagen trots vetskap om växtlokalen!</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2421,12 +2211,7 @@
         <v>108193277</v>
       </c>
       <c r="B16" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2470,10 +2255,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550645.2812275626</v>
+        <v>550645</v>
       </c>
       <c r="R16" t="n">
-        <v>6386009.165194964</v>
+        <v>6386009</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2503,19 +2288,9 @@
           <t>2023-04-16</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-04-16</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">

--- a/artfynd/A 2518-2023 artfynd.xlsx
+++ b/artfynd/A 2518-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908131</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908150</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908159</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908167</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908179</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908189</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908197</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1544,6 +1584,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908213</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908224</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1760,6 +1810,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908234</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1870,6 +1925,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106908261</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1980,6 +2040,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108193121</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2090,6 +2155,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108193178</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2205,6 +2275,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108193455</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2320,8 +2395,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108193277</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>